--- a/tools/Misc/gw.xlsx
+++ b/tools/Misc/gw.xlsx
@@ -98,12 +98,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -570,355 +571,355 @@
                   <c:v>710.14</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>718.31</c:v>
+                  <c:v>711.30714285714294</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>725.32</c:v>
+                  <c:v>719.31142857142856</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>730.19</c:v>
+                  <c:v>726.01571428571424</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>732.37</c:v>
+                  <c:v>730.50142857142851</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>732.1</c:v>
+                  <c:v>732.33142857142855</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>729.17</c:v>
+                  <c:v>731.68142857142857</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>724.69</c:v>
+                  <c:v>728.53</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>719.68</c:v>
+                  <c:v>723.97428571428577</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>715.13</c:v>
+                  <c:v>719.03</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>712.15</c:v>
+                  <c:v>714.70428571428579</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>710.54</c:v>
+                  <c:v>711.92</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>710.6</c:v>
+                  <c:v>710.54857142857134</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>711.88</c:v>
+                  <c:v>710.78285714285721</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>713.64</c:v>
+                  <c:v>712.13142857142861</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>715.36</c:v>
+                  <c:v>713.88571428571424</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>715.62</c:v>
+                  <c:v>715.39714285714285</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>714.25</c:v>
+                  <c:v>715.4242857142857</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>711.17</c:v>
+                  <c:v>713.81000000000006</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>706.74</c:v>
+                  <c:v>710.53714285714284</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>702.02</c:v>
+                  <c:v>706.06571428571431</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>697.38</c:v>
+                  <c:v>701.35714285714289</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>694.15</c:v>
+                  <c:v>696.91857142857145</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>693.19</c:v>
+                  <c:v>694.01285714285711</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>694.98</c:v>
+                  <c:v>693.44571428571442</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>699.82</c:v>
+                  <c:v>695.67142857142858</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>706.62</c:v>
+                  <c:v>700.7914285714287</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>714.76</c:v>
+                  <c:v>707.7828571428571</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>723.07</c:v>
+                  <c:v>715.94714285714281</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>730.36</c:v>
+                  <c:v>724.11142857142863</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>735.94</c:v>
+                  <c:v>731.15714285714296</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>738.54</c:v>
+                  <c:v>736.31142857142856</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>738.32</c:v>
+                  <c:v>738.50857142857137</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>735.66</c:v>
+                  <c:v>737.94</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>731.3</c:v>
+                  <c:v>735.03714285714284</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>726.58</c:v>
+                  <c:v>730.62571428571425</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>721.87</c:v>
+                  <c:v>725.90714285714284</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>718.34</c:v>
+                  <c:v>721.36571428571426</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>716.47</c:v>
+                  <c:v>718.07285714285717</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>716.3</c:v>
+                  <c:v>716.4457142857143</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>717.78</c:v>
+                  <c:v>716.51142857142861</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>719.54</c:v>
+                  <c:v>718.03142857142859</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>721.05</c:v>
+                  <c:v>719.75571428571425</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>721.52</c:v>
+                  <c:v>721.11714285714288</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>720.38</c:v>
+                  <c:v>721.35714285714278</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>717.82</c:v>
+                  <c:v>720.01428571428573</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>713.51</c:v>
+                  <c:v>717.20428571428579</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>708.47</c:v>
+                  <c:v>712.79000000000008</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>703.66</c:v>
+                  <c:v>707.78285714285721</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>700.15</c:v>
+                  <c:v>703.15857142857146</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>699.13</c:v>
+                  <c:v>700.00428571428563</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>700.53</c:v>
+                  <c:v>699.33</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>704.74</c:v>
+                  <c:v>701.1314285714285</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>711.33</c:v>
+                  <c:v>705.68142857142857</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>719.41</c:v>
+                  <c:v>712.48428571428576</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>728.16</c:v>
+                  <c:v>720.66</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>735.72</c:v>
+                  <c:v>729.2399999999999</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>741.36</c:v>
+                  <c:v>736.52571428571434</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>744.37</c:v>
+                  <c:v>741.79000000000008</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>744.55</c:v>
+                  <c:v>744.39571428571435</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>742.49</c:v>
+                  <c:v>744.25571428571425</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>738.28</c:v>
+                  <c:v>741.88857142857148</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>733.22</c:v>
+                  <c:v>737.55714285714282</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>728.37</c:v>
+                  <c:v>732.52714285714285</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>724.61</c:v>
+                  <c:v>727.83285714285716</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>722.79</c:v>
+                  <c:v>724.35</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>722.4</c:v>
+                  <c:v>722.73428571428565</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>723.42</c:v>
+                  <c:v>722.54571428571421</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>725.16</c:v>
+                  <c:v>723.66857142857134</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>726.78</c:v>
+                  <c:v>725.39142857142861</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>727.75</c:v>
+                  <c:v>726.91857142857134</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>726.85</c:v>
+                  <c:v>727.62142857142851</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>724.19</c:v>
+                  <c:v>726.47</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>720.01</c:v>
+                  <c:v>723.59285714285716</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>714.97</c:v>
+                  <c:v>719.29</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>710.35</c:v>
+                  <c:v>714.31000000000006</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>706.56</c:v>
+                  <c:v>709.80857142857144</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>704.87</c:v>
+                  <c:v>706.31857142857132</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>705.88</c:v>
+                  <c:v>705.01428571428585</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>709.75</c:v>
+                  <c:v>706.43285714285707</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>716.41</c:v>
+                  <c:v>710.70142857142866</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>724.41</c:v>
+                  <c:v>717.55285714285708</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>732.94</c:v>
+                  <c:v>725.62857142857138</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>740.76</c:v>
+                  <c:v>734.05714285714294</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>746.77</c:v>
+                  <c:v>741.6185714285715</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>750.53</c:v>
+                  <c:v>747.30714285714282</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>751.1</c:v>
+                  <c:v>750.61142857142852</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>749.02</c:v>
+                  <c:v>750.80285714285719</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>744.98</c:v>
+                  <c:v>748.44285714285718</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>739.94</c:v>
+                  <c:v>744.26</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>735.28</c:v>
+                  <c:v>739.27428571428572</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>731.29</c:v>
+                  <c:v>734.70999999999992</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>728.89</c:v>
+                  <c:v>730.94714285714281</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>728.26</c:v>
+                  <c:v>728.8</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>729.12</c:v>
+                  <c:v>728.38285714285723</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>731.15</c:v>
+                  <c:v>729.41</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>732.85</c:v>
+                  <c:v>731.39285714285722</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>733.69</c:v>
+                  <c:v>732.97</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>733.02</c:v>
+                  <c:v>733.59428571428577</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>730.59</c:v>
+                  <c:v>732.67285714285708</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>726.87</c:v>
+                  <c:v>730.05857142857144</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>721.86</c:v>
+                  <c:v>726.15428571428572</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>716.8</c:v>
+                  <c:v>721.13714285714286</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>712.76</c:v>
+                  <c:v>716.22285714285715</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>710.71</c:v>
+                  <c:v>712.4671428571429</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>711.64</c:v>
+                  <c:v>710.84285714285716</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>715.15</c:v>
+                  <c:v>712.14142857142861</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>721.24</c:v>
+                  <c:v>716.02</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>729.14</c:v>
+                  <c:v>722.3685714285715</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>737.74</c:v>
+                  <c:v>730.36857142857139</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>746.12</c:v>
+                  <c:v>738.93714285714282</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>752.49</c:v>
+                  <c:v>747.03</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>756.35</c:v>
+                  <c:v>753.04142857142847</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>757.32</c:v>
+                  <c:v>756.48857142857139</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>755.57</c:v>
+                  <c:v>757.07</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>752.05</c:v>
+                  <c:v>755.06714285714293</c:v>
                 </c:pt>
                 <c:pt idx="116">
-                  <c:v>747.04</c:v>
+                  <c:v>751.33428571428567</c:v>
                 </c:pt>
                 <c:pt idx="117">
-                  <c:v>741.95</c:v>
+                  <c:v>746.31285714285718</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1684,16 +1685,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>576775</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>450167</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>21101</xdr:rowOff>
+      <xdr:rowOff>63304</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>492371</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>365763</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>105507</xdr:rowOff>
+      <xdr:rowOff>147710</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2012,7 +2013,8 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.5625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.97265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.97265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -2036,7 +2038,7 @@
         <v>46133</v>
       </c>
       <c r="B3">
-        <v>718.31</v>
+        <v>711.30714285714294</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -2044,7 +2046,7 @@
         <v>46134</v>
       </c>
       <c r="B4">
-        <v>725.32</v>
+        <v>719.31142857142856</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -2052,7 +2054,7 @@
         <v>46135</v>
       </c>
       <c r="B5">
-        <v>730.19</v>
+        <v>726.01571428571424</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -2060,7 +2062,7 @@
         <v>46136</v>
       </c>
       <c r="B6">
-        <v>732.37</v>
+        <v>730.50142857142851</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -2068,7 +2070,7 @@
         <v>46139</v>
       </c>
       <c r="B7">
-        <v>732.1</v>
+        <v>732.33142857142855</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -2076,7 +2078,7 @@
         <v>46140</v>
       </c>
       <c r="B8">
-        <v>729.17</v>
+        <v>731.68142857142857</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -2084,7 +2086,7 @@
         <v>46141</v>
       </c>
       <c r="B9">
-        <v>724.69</v>
+        <v>728.53</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -2092,7 +2094,7 @@
         <v>46142</v>
       </c>
       <c r="B10">
-        <v>719.68</v>
+        <v>723.97428571428577</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -2100,7 +2102,7 @@
         <v>46143</v>
       </c>
       <c r="B11">
-        <v>715.13</v>
+        <v>719.03</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -2108,9 +2110,9 @@
         <v>46146</v>
       </c>
       <c r="B12">
-        <v>712.15</v>
-      </c>
-      <c r="C12" t="s">
+        <v>714.70428571428579</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>2</v>
       </c>
     </row>
@@ -2119,7 +2121,7 @@
         <v>46147</v>
       </c>
       <c r="B13">
-        <v>710.54</v>
+        <v>711.92</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -2127,7 +2129,7 @@
         <v>46148</v>
       </c>
       <c r="B14">
-        <v>710.6</v>
+        <v>710.54857142857134</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -2135,7 +2137,7 @@
         <v>46149</v>
       </c>
       <c r="B15">
-        <v>711.88</v>
+        <v>710.78285714285721</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -2143,7 +2145,7 @@
         <v>46150</v>
       </c>
       <c r="B16">
-        <v>713.64</v>
+        <v>712.13142857142861</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
@@ -2151,7 +2153,7 @@
         <v>46153</v>
       </c>
       <c r="B17">
-        <v>715.36</v>
+        <v>713.88571428571424</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
@@ -2159,7 +2161,7 @@
         <v>46154</v>
       </c>
       <c r="B18">
-        <v>715.62</v>
+        <v>715.39714285714285</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
@@ -2167,7 +2169,7 @@
         <v>46155</v>
       </c>
       <c r="B19">
-        <v>714.25</v>
+        <v>715.4242857142857</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
@@ -2175,7 +2177,7 @@
         <v>46156</v>
       </c>
       <c r="B20">
-        <v>711.17</v>
+        <v>713.81000000000006</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
@@ -2183,7 +2185,7 @@
         <v>46157</v>
       </c>
       <c r="B21">
-        <v>706.74</v>
+        <v>710.53714285714284</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
@@ -2191,7 +2193,7 @@
         <v>46160</v>
       </c>
       <c r="B22">
-        <v>702.02</v>
+        <v>706.06571428571431</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
@@ -2199,7 +2201,7 @@
         <v>46161</v>
       </c>
       <c r="B23">
-        <v>697.38</v>
+        <v>701.35714285714289</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
@@ -2207,7 +2209,7 @@
         <v>46162</v>
       </c>
       <c r="B24">
-        <v>694.15</v>
+        <v>696.91857142857145</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
@@ -2215,7 +2217,7 @@
         <v>46163</v>
       </c>
       <c r="B25">
-        <v>693.19</v>
+        <v>694.01285714285711</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
@@ -2223,7 +2225,7 @@
         <v>46164</v>
       </c>
       <c r="B26">
-        <v>694.98</v>
+        <v>693.44571428571442</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
@@ -2231,7 +2233,7 @@
         <v>46167</v>
       </c>
       <c r="B27">
-        <v>699.82</v>
+        <v>695.67142857142858</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
@@ -2239,7 +2241,7 @@
         <v>46168</v>
       </c>
       <c r="B28">
-        <v>706.62</v>
+        <v>700.7914285714287</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
@@ -2247,7 +2249,7 @@
         <v>46169</v>
       </c>
       <c r="B29">
-        <v>714.76</v>
+        <v>707.7828571428571</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
@@ -2255,7 +2257,7 @@
         <v>46170</v>
       </c>
       <c r="B30">
-        <v>723.07</v>
+        <v>715.94714285714281</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
@@ -2263,7 +2265,7 @@
         <v>46171</v>
       </c>
       <c r="B31">
-        <v>730.36</v>
+        <v>724.11142857142863</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
@@ -2271,7 +2273,7 @@
         <v>46174</v>
       </c>
       <c r="B32">
-        <v>735.94</v>
+        <v>731.15714285714296</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
@@ -2279,7 +2281,7 @@
         <v>46175</v>
       </c>
       <c r="B33">
-        <v>738.54</v>
+        <v>736.31142857142856</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
@@ -2287,7 +2289,7 @@
         <v>46176</v>
       </c>
       <c r="B34">
-        <v>738.32</v>
+        <v>738.50857142857137</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
@@ -2295,7 +2297,7 @@
         <v>46177</v>
       </c>
       <c r="B35">
-        <v>735.66</v>
+        <v>737.94</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
@@ -2303,7 +2305,7 @@
         <v>46178</v>
       </c>
       <c r="B36">
-        <v>731.3</v>
+        <v>735.03714285714284</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
@@ -2311,7 +2313,7 @@
         <v>46181</v>
       </c>
       <c r="B37">
-        <v>726.58</v>
+        <v>730.62571428571425</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
@@ -2319,7 +2321,7 @@
         <v>46182</v>
       </c>
       <c r="B38">
-        <v>721.87</v>
+        <v>725.90714285714284</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
@@ -2327,7 +2329,7 @@
         <v>46183</v>
       </c>
       <c r="B39">
-        <v>718.34</v>
+        <v>721.36571428571426</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
@@ -2335,7 +2337,7 @@
         <v>46184</v>
       </c>
       <c r="B40">
-        <v>716.47</v>
+        <v>718.07285714285717</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
@@ -2343,7 +2345,7 @@
         <v>46185</v>
       </c>
       <c r="B41">
-        <v>716.3</v>
+        <v>716.4457142857143</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
@@ -2351,7 +2353,7 @@
         <v>46188</v>
       </c>
       <c r="B42">
-        <v>717.78</v>
+        <v>716.51142857142861</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
@@ -2359,7 +2361,7 @@
         <v>46189</v>
       </c>
       <c r="B43">
-        <v>719.54</v>
+        <v>718.03142857142859</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
@@ -2367,7 +2369,7 @@
         <v>46190</v>
       </c>
       <c r="B44">
-        <v>721.05</v>
+        <v>719.75571428571425</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
@@ -2375,7 +2377,7 @@
         <v>46191</v>
       </c>
       <c r="B45">
-        <v>721.52</v>
+        <v>721.11714285714288</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
@@ -2383,7 +2385,7 @@
         <v>46192</v>
       </c>
       <c r="B46">
-        <v>720.38</v>
+        <v>721.35714285714278</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
@@ -2391,7 +2393,7 @@
         <v>46195</v>
       </c>
       <c r="B47">
-        <v>717.82</v>
+        <v>720.01428571428573</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
@@ -2399,7 +2401,7 @@
         <v>46196</v>
       </c>
       <c r="B48">
-        <v>713.51</v>
+        <v>717.20428571428579</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
@@ -2407,7 +2409,7 @@
         <v>46197</v>
       </c>
       <c r="B49">
-        <v>708.47</v>
+        <v>712.79000000000008</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
@@ -2415,7 +2417,7 @@
         <v>46198</v>
       </c>
       <c r="B50">
-        <v>703.66</v>
+        <v>707.78285714285721</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
@@ -2423,7 +2425,7 @@
         <v>46199</v>
       </c>
       <c r="B51">
-        <v>700.15</v>
+        <v>703.15857142857146</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
@@ -2431,7 +2433,7 @@
         <v>46202</v>
       </c>
       <c r="B52">
-        <v>699.13</v>
+        <v>700.00428571428563</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.2">
@@ -2439,7 +2441,7 @@
         <v>46203</v>
       </c>
       <c r="B53">
-        <v>700.53</v>
+        <v>699.33</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.2">
@@ -2447,7 +2449,7 @@
         <v>46204</v>
       </c>
       <c r="B54">
-        <v>704.74</v>
+        <v>701.1314285714285</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.2">
@@ -2455,7 +2457,7 @@
         <v>46205</v>
       </c>
       <c r="B55">
-        <v>711.33</v>
+        <v>705.68142857142857</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.2">
@@ -2463,7 +2465,7 @@
         <v>46206</v>
       </c>
       <c r="B56">
-        <v>719.41</v>
+        <v>712.48428571428576</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.2">
@@ -2471,7 +2473,7 @@
         <v>46209</v>
       </c>
       <c r="B57">
-        <v>728.16</v>
+        <v>720.66</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.2">
@@ -2479,7 +2481,7 @@
         <v>46210</v>
       </c>
       <c r="B58">
-        <v>735.72</v>
+        <v>729.2399999999999</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.2">
@@ -2487,7 +2489,7 @@
         <v>46211</v>
       </c>
       <c r="B59">
-        <v>741.36</v>
+        <v>736.52571428571434</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.2">
@@ -2495,7 +2497,7 @@
         <v>46212</v>
       </c>
       <c r="B60">
-        <v>744.37</v>
+        <v>741.79000000000008</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.2">
@@ -2503,7 +2505,7 @@
         <v>46213</v>
       </c>
       <c r="B61">
-        <v>744.55</v>
+        <v>744.39571428571435</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.2">
@@ -2511,7 +2513,7 @@
         <v>46216</v>
       </c>
       <c r="B62">
-        <v>742.49</v>
+        <v>744.25571428571425</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.2">
@@ -2519,7 +2521,7 @@
         <v>46217</v>
       </c>
       <c r="B63">
-        <v>738.28</v>
+        <v>741.88857142857148</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.2">
@@ -2527,7 +2529,7 @@
         <v>46218</v>
       </c>
       <c r="B64">
-        <v>733.22</v>
+        <v>737.55714285714282</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.2">
@@ -2535,7 +2537,7 @@
         <v>46219</v>
       </c>
       <c r="B65">
-        <v>728.37</v>
+        <v>732.52714285714285</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.2">
@@ -2543,7 +2545,7 @@
         <v>46220</v>
       </c>
       <c r="B66">
-        <v>724.61</v>
+        <v>727.83285714285716</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.2">
@@ -2551,7 +2553,7 @@
         <v>46223</v>
       </c>
       <c r="B67">
-        <v>722.79</v>
+        <v>724.35</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.2">
@@ -2559,7 +2561,7 @@
         <v>46224</v>
       </c>
       <c r="B68">
-        <v>722.4</v>
+        <v>722.73428571428565</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.2">
@@ -2567,7 +2569,7 @@
         <v>46225</v>
       </c>
       <c r="B69">
-        <v>723.42</v>
+        <v>722.54571428571421</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.2">
@@ -2575,7 +2577,7 @@
         <v>46226</v>
       </c>
       <c r="B70">
-        <v>725.16</v>
+        <v>723.66857142857134</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.2">
@@ -2583,7 +2585,7 @@
         <v>46227</v>
       </c>
       <c r="B71">
-        <v>726.78</v>
+        <v>725.39142857142861</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.2">
@@ -2591,7 +2593,7 @@
         <v>46230</v>
       </c>
       <c r="B72">
-        <v>727.75</v>
+        <v>726.91857142857134</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.2">
@@ -2599,7 +2601,7 @@
         <v>46231</v>
       </c>
       <c r="B73">
-        <v>726.85</v>
+        <v>727.62142857142851</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.2">
@@ -2607,7 +2609,7 @@
         <v>46232</v>
       </c>
       <c r="B74">
-        <v>724.19</v>
+        <v>726.47</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.2">
@@ -2615,7 +2617,7 @@
         <v>46233</v>
       </c>
       <c r="B75">
-        <v>720.01</v>
+        <v>723.59285714285716</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.2">
@@ -2623,7 +2625,7 @@
         <v>46234</v>
       </c>
       <c r="B76">
-        <v>714.97</v>
+        <v>719.29</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.2">
@@ -2631,7 +2633,7 @@
         <v>46237</v>
       </c>
       <c r="B77">
-        <v>710.35</v>
+        <v>714.31000000000006</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.2">
@@ -2639,7 +2641,7 @@
         <v>46238</v>
       </c>
       <c r="B78">
-        <v>706.56</v>
+        <v>709.80857142857144</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.2">
@@ -2647,7 +2649,7 @@
         <v>46239</v>
       </c>
       <c r="B79">
-        <v>704.87</v>
+        <v>706.31857142857132</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.2">
@@ -2655,7 +2657,7 @@
         <v>46240</v>
       </c>
       <c r="B80">
-        <v>705.88</v>
+        <v>705.01428571428585</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.2">
@@ -2663,7 +2665,7 @@
         <v>46241</v>
       </c>
       <c r="B81">
-        <v>709.75</v>
+        <v>706.43285714285707</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.2">
@@ -2671,7 +2673,7 @@
         <v>46244</v>
       </c>
       <c r="B82">
-        <v>716.41</v>
+        <v>710.70142857142866</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.2">
@@ -2679,7 +2681,7 @@
         <v>46245</v>
       </c>
       <c r="B83">
-        <v>724.41</v>
+        <v>717.55285714285708</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.2">
@@ -2687,7 +2689,7 @@
         <v>46246</v>
       </c>
       <c r="B84">
-        <v>732.94</v>
+        <v>725.62857142857138</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.2">
@@ -2695,7 +2697,7 @@
         <v>46247</v>
       </c>
       <c r="B85">
-        <v>740.76</v>
+        <v>734.05714285714294</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.2">
@@ -2703,7 +2705,7 @@
         <v>46248</v>
       </c>
       <c r="B86">
-        <v>746.77</v>
+        <v>741.6185714285715</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.2">
@@ -2711,7 +2713,7 @@
         <v>46251</v>
       </c>
       <c r="B87">
-        <v>750.53</v>
+        <v>747.30714285714282</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.2">
@@ -2719,7 +2721,7 @@
         <v>46252</v>
       </c>
       <c r="B88">
-        <v>751.1</v>
+        <v>750.61142857142852</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.2">
@@ -2727,7 +2729,7 @@
         <v>46253</v>
       </c>
       <c r="B89">
-        <v>749.02</v>
+        <v>750.80285714285719</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.2">
@@ -2735,7 +2737,7 @@
         <v>46254</v>
       </c>
       <c r="B90">
-        <v>744.98</v>
+        <v>748.44285714285718</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.2">
@@ -2743,7 +2745,7 @@
         <v>46255</v>
       </c>
       <c r="B91">
-        <v>739.94</v>
+        <v>744.26</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.2">
@@ -2751,7 +2753,7 @@
         <v>46258</v>
       </c>
       <c r="B92">
-        <v>735.28</v>
+        <v>739.27428571428572</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.2">
@@ -2759,7 +2761,7 @@
         <v>46259</v>
       </c>
       <c r="B93">
-        <v>731.29</v>
+        <v>734.70999999999992</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.2">
@@ -2767,7 +2769,7 @@
         <v>46260</v>
       </c>
       <c r="B94">
-        <v>728.89</v>
+        <v>730.94714285714281</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.2">
@@ -2775,7 +2777,7 @@
         <v>46261</v>
       </c>
       <c r="B95">
-        <v>728.26</v>
+        <v>728.8</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.2">
@@ -2783,7 +2785,7 @@
         <v>46262</v>
       </c>
       <c r="B96">
-        <v>729.12</v>
+        <v>728.38285714285723</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.2">
@@ -2791,7 +2793,7 @@
         <v>46265</v>
       </c>
       <c r="B97">
-        <v>731.15</v>
+        <v>729.41</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.2">
@@ -2799,7 +2801,7 @@
         <v>46266</v>
       </c>
       <c r="B98">
-        <v>732.85</v>
+        <v>731.39285714285722</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.2">
@@ -2807,7 +2809,7 @@
         <v>46267</v>
       </c>
       <c r="B99">
-        <v>733.69</v>
+        <v>732.97</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.2">
@@ -2815,7 +2817,7 @@
         <v>46268</v>
       </c>
       <c r="B100">
-        <v>733.02</v>
+        <v>733.59428571428577</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.2">
@@ -2823,7 +2825,7 @@
         <v>46269</v>
       </c>
       <c r="B101">
-        <v>730.59</v>
+        <v>732.67285714285708</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.2">
@@ -2831,7 +2833,7 @@
         <v>46272</v>
       </c>
       <c r="B102">
-        <v>726.87</v>
+        <v>730.05857142857144</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.2">
@@ -2839,7 +2841,7 @@
         <v>46273</v>
       </c>
       <c r="B103">
-        <v>721.86</v>
+        <v>726.15428571428572</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.2">
@@ -2847,7 +2849,7 @@
         <v>46274</v>
       </c>
       <c r="B104">
-        <v>716.8</v>
+        <v>721.13714285714286</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.2">
@@ -2855,7 +2857,7 @@
         <v>46275</v>
       </c>
       <c r="B105">
-        <v>712.76</v>
+        <v>716.22285714285715</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.2">
@@ -2863,7 +2865,7 @@
         <v>46276</v>
       </c>
       <c r="B106">
-        <v>710.71</v>
+        <v>712.4671428571429</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.2">
@@ -2871,7 +2873,7 @@
         <v>46279</v>
       </c>
       <c r="B107">
-        <v>711.64</v>
+        <v>710.84285714285716</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.2">
@@ -2879,7 +2881,7 @@
         <v>46280</v>
       </c>
       <c r="B108">
-        <v>715.15</v>
+        <v>712.14142857142861</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.2">
@@ -2887,7 +2889,7 @@
         <v>46281</v>
       </c>
       <c r="B109">
-        <v>721.24</v>
+        <v>716.02</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.2">
@@ -2895,7 +2897,7 @@
         <v>46282</v>
       </c>
       <c r="B110">
-        <v>729.14</v>
+        <v>722.3685714285715</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.2">
@@ -2903,7 +2905,7 @@
         <v>46283</v>
       </c>
       <c r="B111">
-        <v>737.74</v>
+        <v>730.36857142857139</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.2">
@@ -2911,67 +2913,63 @@
         <v>46286</v>
       </c>
       <c r="B112">
-        <v>746.12</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.2">
+        <v>738.93714285714282</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A113" s="2">
         <v>46287</v>
       </c>
       <c r="B113">
-        <v>752.49</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.2">
+        <v>747.03</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A114" s="2">
         <v>46288</v>
       </c>
       <c r="B114">
-        <v>756.35</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.2">
+        <v>753.04142857142847</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A115" s="2">
         <v>46289</v>
       </c>
       <c r="B115">
-        <v>757.32</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.2">
+        <v>756.48857142857139</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A116" s="2">
         <v>46290</v>
       </c>
       <c r="B116">
-        <v>755.57</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.2">
+        <v>757.07</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A117" s="2">
         <v>46293</v>
       </c>
       <c r="B117">
-        <v>752.05</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.2">
+        <v>755.06714285714293</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A118" s="2">
         <v>46294</v>
       </c>
       <c r="B118">
-        <v>747.04</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.2">
+        <v>751.33428571428567</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A119" s="2">
         <v>46295</v>
       </c>
       <c r="B119">
-        <v>741.95</v>
-      </c>
-      <c r="C119">
-        <f>CORREL(B2:B116,B5:B119)</f>
-        <v>0.66190756901938497</v>
+        <v>746.31285714285718</v>
       </c>
     </row>
   </sheetData>

--- a/tools/Misc/gw.xlsx
+++ b/tools/Misc/gw.xlsx
@@ -563,10 +563,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$119</c:f>
+              <c:f>Sheet1!$B$2:$B$111</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="118"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>710.14</c:v>
                 </c:pt>
@@ -574,351 +574,327 @@
                   <c:v>711.30714285714294</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>719.31142857142856</c:v>
+                  <c:v>714.70428571428579</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>726.01571428571424</c:v>
+                  <c:v>711.92</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>730.50142857142851</c:v>
+                  <c:v>710.54857142857134</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>732.33142857142855</c:v>
+                  <c:v>710.78285714285721</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>731.68142857142857</c:v>
+                  <c:v>712.13142857142861</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>728.53</c:v>
+                  <c:v>713.88571428571424</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>723.97428571428577</c:v>
+                  <c:v>715.39714285714285</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>719.03</c:v>
+                  <c:v>715.4242857142857</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>714.70428571428579</c:v>
+                  <c:v>713.81000000000006</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>711.92</c:v>
+                  <c:v>710.53714285714284</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>710.54857142857134</c:v>
+                  <c:v>706.06571428571431</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>710.78285714285721</c:v>
+                  <c:v>701.35714285714289</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>712.13142857142861</c:v>
+                  <c:v>696.91857142857145</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>713.88571428571424</c:v>
+                  <c:v>694.01285714285711</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>715.39714285714285</c:v>
+                  <c:v>693.44571428571442</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>715.4242857142857</c:v>
+                  <c:v>695.67142857142858</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>713.81000000000006</c:v>
+                  <c:v>700.7914285714287</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>710.53714285714284</c:v>
+                  <c:v>707.7828571428571</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>706.06571428571431</c:v>
+                  <c:v>715.94714285714281</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>701.35714285714289</c:v>
+                  <c:v>724.11142857142863</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>696.91857142857145</c:v>
+                  <c:v>731.15714285714296</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>694.01285714285711</c:v>
+                  <c:v>736.31142857142856</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>693.44571428571442</c:v>
+                  <c:v>738.50857142857137</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>695.67142857142858</c:v>
+                  <c:v>737.94</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>700.7914285714287</c:v>
+                  <c:v>735.03714285714284</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>707.7828571428571</c:v>
+                  <c:v>730.62571428571425</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>715.94714285714281</c:v>
+                  <c:v>725.90714285714284</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>724.11142857142863</c:v>
+                  <c:v>721.36571428571426</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>731.15714285714296</c:v>
+                  <c:v>718.07285714285717</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>736.31142857142856</c:v>
+                  <c:v>716.4457142857143</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>738.50857142857137</c:v>
+                  <c:v>716.51142857142861</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>737.94</c:v>
+                  <c:v>718.03142857142859</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>735.03714285714284</c:v>
+                  <c:v>719.75571428571425</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>730.62571428571425</c:v>
+                  <c:v>721.11714285714288</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>725.90714285714284</c:v>
+                  <c:v>721.35714285714278</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>721.36571428571426</c:v>
+                  <c:v>720.01428571428573</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>718.07285714285717</c:v>
+                  <c:v>717.20428571428579</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>716.4457142857143</c:v>
+                  <c:v>712.79000000000008</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>716.51142857142861</c:v>
+                  <c:v>707.78285714285721</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>718.03142857142859</c:v>
+                  <c:v>703.15857142857146</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>719.75571428571425</c:v>
+                  <c:v>700.00428571428563</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>721.11714285714288</c:v>
+                  <c:v>699.33</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>721.35714285714278</c:v>
+                  <c:v>701.1314285714285</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>720.01428571428573</c:v>
+                  <c:v>705.68142857142857</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>717.20428571428579</c:v>
+                  <c:v>712.48428571428576</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>712.79000000000008</c:v>
+                  <c:v>720.66</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>707.78285714285721</c:v>
+                  <c:v>729.2399999999999</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>703.15857142857146</c:v>
+                  <c:v>736.52571428571434</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>700.00428571428563</c:v>
+                  <c:v>741.79000000000008</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>699.33</c:v>
+                  <c:v>744.39571428571435</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>701.1314285714285</c:v>
+                  <c:v>744.25571428571425</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>705.68142857142857</c:v>
+                  <c:v>741.88857142857148</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>712.48428571428576</c:v>
+                  <c:v>737.55714285714282</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>720.66</c:v>
+                  <c:v>732.52714285714285</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>729.2399999999999</c:v>
+                  <c:v>727.83285714285716</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>736.52571428571434</c:v>
+                  <c:v>724.35</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>741.79000000000008</c:v>
+                  <c:v>722.73428571428565</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>744.39571428571435</c:v>
+                  <c:v>722.54571428571421</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>744.25571428571425</c:v>
+                  <c:v>723.66857142857134</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>741.88857142857148</c:v>
+                  <c:v>725.39142857142861</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>737.55714285714282</c:v>
+                  <c:v>726.91857142857134</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>732.52714285714285</c:v>
+                  <c:v>727.62142857142851</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>727.83285714285716</c:v>
+                  <c:v>726.47</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>724.35</c:v>
+                  <c:v>723.59285714285716</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>722.73428571428565</c:v>
+                  <c:v>719.29</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>722.54571428571421</c:v>
+                  <c:v>714.31000000000006</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>723.66857142857134</c:v>
+                  <c:v>709.80857142857144</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>725.39142857142861</c:v>
+                  <c:v>706.31857142857132</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>726.91857142857134</c:v>
+                  <c:v>705.01428571428585</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>727.62142857142851</c:v>
+                  <c:v>706.43285714285707</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>726.47</c:v>
+                  <c:v>710.70142857142866</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>723.59285714285716</c:v>
+                  <c:v>717.55285714285708</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>719.29</c:v>
+                  <c:v>725.62857142857138</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>714.31000000000006</c:v>
+                  <c:v>734.05714285714294</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>709.80857142857144</c:v>
+                  <c:v>741.6185714285715</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>706.31857142857132</c:v>
+                  <c:v>747.30714285714282</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>705.01428571428585</c:v>
+                  <c:v>750.61142857142852</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>706.43285714285707</c:v>
+                  <c:v>750.80285714285719</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>710.70142857142866</c:v>
+                  <c:v>748.44285714285718</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>717.55285714285708</c:v>
+                  <c:v>744.26</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>725.62857142857138</c:v>
+                  <c:v>739.27428571428572</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>734.05714285714294</c:v>
+                  <c:v>734.70999999999992</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>741.6185714285715</c:v>
+                  <c:v>730.94714285714281</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>747.30714285714282</c:v>
+                  <c:v>728.8</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>750.61142857142852</c:v>
+                  <c:v>728.38285714285723</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>750.80285714285719</c:v>
+                  <c:v>729.41</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>748.44285714285718</c:v>
+                  <c:v>731.39285714285722</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>744.26</c:v>
+                  <c:v>732.97</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>739.27428571428572</c:v>
+                  <c:v>733.59428571428577</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>734.70999999999992</c:v>
+                  <c:v>732.67285714285708</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>730.94714285714281</c:v>
+                  <c:v>730.05857142857144</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>728.8</c:v>
+                  <c:v>726.15428571428572</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>728.38285714285723</c:v>
+                  <c:v>721.13714285714286</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>729.41</c:v>
+                  <c:v>716.22285714285715</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>731.39285714285722</c:v>
+                  <c:v>712.4671428571429</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>732.97</c:v>
+                  <c:v>710.84285714285716</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>733.59428571428577</c:v>
+                  <c:v>712.14142857142861</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>732.67285714285708</c:v>
+                  <c:v>716.02</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>730.05857142857144</c:v>
+                  <c:v>722.3685714285715</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>726.15428571428572</c:v>
+                  <c:v>730.36857142857139</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>721.13714285714286</c:v>
+                  <c:v>738.93714285714282</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>716.22285714285715</c:v>
+                  <c:v>747.03</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>712.4671428571429</c:v>
+                  <c:v>753.04142857142847</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>710.84285714285716</c:v>
+                  <c:v>756.48857142857139</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>712.14142857142861</c:v>
+                  <c:v>757.07</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>716.02</c:v>
+                  <c:v>755.06714285714293</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>722.3685714285715</c:v>
+                  <c:v>751.33428571428567</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>730.36857142857139</c:v>
-                </c:pt>
-                <c:pt idx="110">
-                  <c:v>738.93714285714282</c:v>
-                </c:pt>
-                <c:pt idx="111">
-                  <c:v>747.03</c:v>
-                </c:pt>
-                <c:pt idx="112">
-                  <c:v>753.04142857142847</c:v>
-                </c:pt>
-                <c:pt idx="113">
-                  <c:v>756.48857142857139</c:v>
-                </c:pt>
-                <c:pt idx="114">
-                  <c:v>757.07</c:v>
-                </c:pt>
-                <c:pt idx="115">
-                  <c:v>755.06714285714293</c:v>
-                </c:pt>
-                <c:pt idx="116">
-                  <c:v>751.33428571428567</c:v>
-                </c:pt>
-                <c:pt idx="117">
                   <c:v>746.31285714285718</c:v>
                 </c:pt>
               </c:numCache>
@@ -2046,7 +2022,7 @@
         <v>46134</v>
       </c>
       <c r="B4">
-        <v>719.31142857142856</v>
+        <v>714.70428571428579</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -2054,7 +2030,7 @@
         <v>46135</v>
       </c>
       <c r="B5">
-        <v>726.01571428571424</v>
+        <v>711.92</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -2062,7 +2038,7 @@
         <v>46136</v>
       </c>
       <c r="B6">
-        <v>730.50142857142851</v>
+        <v>710.54857142857134</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -2070,7 +2046,7 @@
         <v>46139</v>
       </c>
       <c r="B7">
-        <v>732.33142857142855</v>
+        <v>710.78285714285721</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -2078,7 +2054,7 @@
         <v>46140</v>
       </c>
       <c r="B8">
-        <v>731.68142857142857</v>
+        <v>712.13142857142861</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -2086,7 +2062,7 @@
         <v>46141</v>
       </c>
       <c r="B9">
-        <v>728.53</v>
+        <v>713.88571428571424</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -2094,7 +2070,7 @@
         <v>46142</v>
       </c>
       <c r="B10">
-        <v>723.97428571428577</v>
+        <v>715.39714285714285</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -2102,7 +2078,7 @@
         <v>46143</v>
       </c>
       <c r="B11">
-        <v>719.03</v>
+        <v>715.4242857142857</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -2110,7 +2086,7 @@
         <v>46146</v>
       </c>
       <c r="B12">
-        <v>714.70428571428579</v>
+        <v>713.81000000000006</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>2</v>
@@ -2121,7 +2097,7 @@
         <v>46147</v>
       </c>
       <c r="B13">
-        <v>711.92</v>
+        <v>710.53714285714284</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -2129,7 +2105,7 @@
         <v>46148</v>
       </c>
       <c r="B14">
-        <v>710.54857142857134</v>
+        <v>706.06571428571431</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -2137,7 +2113,7 @@
         <v>46149</v>
       </c>
       <c r="B15">
-        <v>710.78285714285721</v>
+        <v>701.35714285714289</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -2145,7 +2121,7 @@
         <v>46150</v>
       </c>
       <c r="B16">
-        <v>712.13142857142861</v>
+        <v>696.91857142857145</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
@@ -2153,7 +2129,7 @@
         <v>46153</v>
       </c>
       <c r="B17">
-        <v>713.88571428571424</v>
+        <v>694.01285714285711</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
@@ -2161,7 +2137,7 @@
         <v>46154</v>
       </c>
       <c r="B18">
-        <v>715.39714285714285</v>
+        <v>693.44571428571442</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
@@ -2169,7 +2145,7 @@
         <v>46155</v>
       </c>
       <c r="B19">
-        <v>715.4242857142857</v>
+        <v>695.67142857142858</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
@@ -2177,7 +2153,7 @@
         <v>46156</v>
       </c>
       <c r="B20">
-        <v>713.81000000000006</v>
+        <v>700.7914285714287</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
@@ -2185,7 +2161,7 @@
         <v>46157</v>
       </c>
       <c r="B21">
-        <v>710.53714285714284</v>
+        <v>707.7828571428571</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
@@ -2193,7 +2169,7 @@
         <v>46160</v>
       </c>
       <c r="B22">
-        <v>706.06571428571431</v>
+        <v>715.94714285714281</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
@@ -2201,7 +2177,7 @@
         <v>46161</v>
       </c>
       <c r="B23">
-        <v>701.35714285714289</v>
+        <v>724.11142857142863</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
@@ -2209,7 +2185,7 @@
         <v>46162</v>
       </c>
       <c r="B24">
-        <v>696.91857142857145</v>
+        <v>731.15714285714296</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
@@ -2217,7 +2193,7 @@
         <v>46163</v>
       </c>
       <c r="B25">
-        <v>694.01285714285711</v>
+        <v>736.31142857142856</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
@@ -2225,7 +2201,7 @@
         <v>46164</v>
       </c>
       <c r="B26">
-        <v>693.44571428571442</v>
+        <v>738.50857142857137</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
@@ -2233,7 +2209,7 @@
         <v>46167</v>
       </c>
       <c r="B27">
-        <v>695.67142857142858</v>
+        <v>737.94</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
@@ -2241,7 +2217,7 @@
         <v>46168</v>
       </c>
       <c r="B28">
-        <v>700.7914285714287</v>
+        <v>735.03714285714284</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
@@ -2249,7 +2225,7 @@
         <v>46169</v>
       </c>
       <c r="B29">
-        <v>707.7828571428571</v>
+        <v>730.62571428571425</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
@@ -2257,7 +2233,7 @@
         <v>46170</v>
       </c>
       <c r="B30">
-        <v>715.94714285714281</v>
+        <v>725.90714285714284</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
@@ -2265,7 +2241,7 @@
         <v>46171</v>
       </c>
       <c r="B31">
-        <v>724.11142857142863</v>
+        <v>721.36571428571426</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
@@ -2273,7 +2249,7 @@
         <v>46174</v>
       </c>
       <c r="B32">
-        <v>731.15714285714296</v>
+        <v>718.07285714285717</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
@@ -2281,7 +2257,7 @@
         <v>46175</v>
       </c>
       <c r="B33">
-        <v>736.31142857142856</v>
+        <v>716.4457142857143</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
@@ -2289,7 +2265,7 @@
         <v>46176</v>
       </c>
       <c r="B34">
-        <v>738.50857142857137</v>
+        <v>716.51142857142861</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
@@ -2297,7 +2273,7 @@
         <v>46177</v>
       </c>
       <c r="B35">
-        <v>737.94</v>
+        <v>718.03142857142859</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
@@ -2305,7 +2281,7 @@
         <v>46178</v>
       </c>
       <c r="B36">
-        <v>735.03714285714284</v>
+        <v>719.75571428571425</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
@@ -2313,7 +2289,7 @@
         <v>46181</v>
       </c>
       <c r="B37">
-        <v>730.62571428571425</v>
+        <v>721.11714285714288</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
@@ -2321,7 +2297,7 @@
         <v>46182</v>
       </c>
       <c r="B38">
-        <v>725.90714285714284</v>
+        <v>721.35714285714278</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
@@ -2329,7 +2305,7 @@
         <v>46183</v>
       </c>
       <c r="B39">
-        <v>721.36571428571426</v>
+        <v>720.01428571428573</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
@@ -2337,7 +2313,7 @@
         <v>46184</v>
       </c>
       <c r="B40">
-        <v>718.07285714285717</v>
+        <v>717.20428571428579</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
@@ -2345,7 +2321,7 @@
         <v>46185</v>
       </c>
       <c r="B41">
-        <v>716.4457142857143</v>
+        <v>712.79000000000008</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
@@ -2353,7 +2329,7 @@
         <v>46188</v>
       </c>
       <c r="B42">
-        <v>716.51142857142861</v>
+        <v>707.78285714285721</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
@@ -2361,7 +2337,7 @@
         <v>46189</v>
       </c>
       <c r="B43">
-        <v>718.03142857142859</v>
+        <v>703.15857142857146</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
@@ -2369,7 +2345,7 @@
         <v>46190</v>
       </c>
       <c r="B44">
-        <v>719.75571428571425</v>
+        <v>700.00428571428563</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
@@ -2377,7 +2353,7 @@
         <v>46191</v>
       </c>
       <c r="B45">
-        <v>721.11714285714288</v>
+        <v>699.33</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
@@ -2385,7 +2361,7 @@
         <v>46192</v>
       </c>
       <c r="B46">
-        <v>721.35714285714278</v>
+        <v>701.1314285714285</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
@@ -2393,7 +2369,7 @@
         <v>46195</v>
       </c>
       <c r="B47">
-        <v>720.01428571428573</v>
+        <v>705.68142857142857</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
@@ -2401,7 +2377,7 @@
         <v>46196</v>
       </c>
       <c r="B48">
-        <v>717.20428571428579</v>
+        <v>712.48428571428576</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
@@ -2409,7 +2385,7 @@
         <v>46197</v>
       </c>
       <c r="B49">
-        <v>712.79000000000008</v>
+        <v>720.66</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
@@ -2417,7 +2393,7 @@
         <v>46198</v>
       </c>
       <c r="B50">
-        <v>707.78285714285721</v>
+        <v>729.2399999999999</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
@@ -2425,7 +2401,7 @@
         <v>46199</v>
       </c>
       <c r="B51">
-        <v>703.15857142857146</v>
+        <v>736.52571428571434</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
@@ -2433,7 +2409,7 @@
         <v>46202</v>
       </c>
       <c r="B52">
-        <v>700.00428571428563</v>
+        <v>741.79000000000008</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.2">
@@ -2441,7 +2417,7 @@
         <v>46203</v>
       </c>
       <c r="B53">
-        <v>699.33</v>
+        <v>744.39571428571435</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.2">
@@ -2449,7 +2425,7 @@
         <v>46204</v>
       </c>
       <c r="B54">
-        <v>701.1314285714285</v>
+        <v>744.25571428571425</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.2">
@@ -2457,7 +2433,7 @@
         <v>46205</v>
       </c>
       <c r="B55">
-        <v>705.68142857142857</v>
+        <v>741.88857142857148</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.2">
@@ -2465,7 +2441,7 @@
         <v>46206</v>
       </c>
       <c r="B56">
-        <v>712.48428571428576</v>
+        <v>737.55714285714282</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.2">
@@ -2473,7 +2449,7 @@
         <v>46209</v>
       </c>
       <c r="B57">
-        <v>720.66</v>
+        <v>732.52714285714285</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.2">
@@ -2481,7 +2457,7 @@
         <v>46210</v>
       </c>
       <c r="B58">
-        <v>729.2399999999999</v>
+        <v>727.83285714285716</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.2">
@@ -2489,7 +2465,7 @@
         <v>46211</v>
       </c>
       <c r="B59">
-        <v>736.52571428571434</v>
+        <v>724.35</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.2">
@@ -2497,7 +2473,7 @@
         <v>46212</v>
       </c>
       <c r="B60">
-        <v>741.79000000000008</v>
+        <v>722.73428571428565</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.2">
@@ -2505,7 +2481,7 @@
         <v>46213</v>
       </c>
       <c r="B61">
-        <v>744.39571428571435</v>
+        <v>722.54571428571421</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.2">
@@ -2513,7 +2489,7 @@
         <v>46216</v>
       </c>
       <c r="B62">
-        <v>744.25571428571425</v>
+        <v>723.66857142857134</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.2">
@@ -2521,7 +2497,7 @@
         <v>46217</v>
       </c>
       <c r="B63">
-        <v>741.88857142857148</v>
+        <v>725.39142857142861</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.2">
@@ -2529,7 +2505,7 @@
         <v>46218</v>
       </c>
       <c r="B64">
-        <v>737.55714285714282</v>
+        <v>726.91857142857134</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.2">
@@ -2537,7 +2513,7 @@
         <v>46219</v>
       </c>
       <c r="B65">
-        <v>732.52714285714285</v>
+        <v>727.62142857142851</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.2">
@@ -2545,7 +2521,7 @@
         <v>46220</v>
       </c>
       <c r="B66">
-        <v>727.83285714285716</v>
+        <v>726.47</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.2">
@@ -2553,7 +2529,7 @@
         <v>46223</v>
       </c>
       <c r="B67">
-        <v>724.35</v>
+        <v>723.59285714285716</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.2">
@@ -2561,7 +2537,7 @@
         <v>46224</v>
       </c>
       <c r="B68">
-        <v>722.73428571428565</v>
+        <v>719.29</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.2">
@@ -2569,7 +2545,7 @@
         <v>46225</v>
       </c>
       <c r="B69">
-        <v>722.54571428571421</v>
+        <v>714.31000000000006</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.2">
@@ -2577,7 +2553,7 @@
         <v>46226</v>
       </c>
       <c r="B70">
-        <v>723.66857142857134</v>
+        <v>709.80857142857144</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.2">
@@ -2585,7 +2561,7 @@
         <v>46227</v>
       </c>
       <c r="B71">
-        <v>725.39142857142861</v>
+        <v>706.31857142857132</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.2">
@@ -2593,7 +2569,7 @@
         <v>46230</v>
       </c>
       <c r="B72">
-        <v>726.91857142857134</v>
+        <v>705.01428571428585</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.2">
@@ -2601,7 +2577,7 @@
         <v>46231</v>
       </c>
       <c r="B73">
-        <v>727.62142857142851</v>
+        <v>706.43285714285707</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.2">
@@ -2609,7 +2585,7 @@
         <v>46232</v>
       </c>
       <c r="B74">
-        <v>726.47</v>
+        <v>710.70142857142866</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.2">
@@ -2617,7 +2593,7 @@
         <v>46233</v>
       </c>
       <c r="B75">
-        <v>723.59285714285716</v>
+        <v>717.55285714285708</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.2">
@@ -2625,7 +2601,7 @@
         <v>46234</v>
       </c>
       <c r="B76">
-        <v>719.29</v>
+        <v>725.62857142857138</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.2">
@@ -2633,7 +2609,7 @@
         <v>46237</v>
       </c>
       <c r="B77">
-        <v>714.31000000000006</v>
+        <v>734.05714285714294</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.2">
@@ -2641,7 +2617,7 @@
         <v>46238</v>
       </c>
       <c r="B78">
-        <v>709.80857142857144</v>
+        <v>741.6185714285715</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.2">
@@ -2649,7 +2625,7 @@
         <v>46239</v>
       </c>
       <c r="B79">
-        <v>706.31857142857132</v>
+        <v>747.30714285714282</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.2">
@@ -2657,7 +2633,7 @@
         <v>46240</v>
       </c>
       <c r="B80">
-        <v>705.01428571428585</v>
+        <v>750.61142857142852</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.2">
@@ -2665,7 +2641,7 @@
         <v>46241</v>
       </c>
       <c r="B81">
-        <v>706.43285714285707</v>
+        <v>750.80285714285719</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.2">
@@ -2673,7 +2649,7 @@
         <v>46244</v>
       </c>
       <c r="B82">
-        <v>710.70142857142866</v>
+        <v>748.44285714285718</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.2">
@@ -2681,7 +2657,7 @@
         <v>46245</v>
       </c>
       <c r="B83">
-        <v>717.55285714285708</v>
+        <v>744.26</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.2">
@@ -2689,7 +2665,7 @@
         <v>46246</v>
       </c>
       <c r="B84">
-        <v>725.62857142857138</v>
+        <v>739.27428571428572</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.2">
@@ -2697,7 +2673,7 @@
         <v>46247</v>
       </c>
       <c r="B85">
-        <v>734.05714285714294</v>
+        <v>734.70999999999992</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.2">
@@ -2705,7 +2681,7 @@
         <v>46248</v>
       </c>
       <c r="B86">
-        <v>741.6185714285715</v>
+        <v>730.94714285714281</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.2">
@@ -2713,7 +2689,7 @@
         <v>46251</v>
       </c>
       <c r="B87">
-        <v>747.30714285714282</v>
+        <v>728.8</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.2">
@@ -2721,7 +2697,7 @@
         <v>46252</v>
       </c>
       <c r="B88">
-        <v>750.61142857142852</v>
+        <v>728.38285714285723</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.2">
@@ -2729,7 +2705,7 @@
         <v>46253</v>
       </c>
       <c r="B89">
-        <v>750.80285714285719</v>
+        <v>729.41</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.2">
@@ -2737,7 +2713,7 @@
         <v>46254</v>
       </c>
       <c r="B90">
-        <v>748.44285714285718</v>
+        <v>731.39285714285722</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.2">
@@ -2745,7 +2721,7 @@
         <v>46255</v>
       </c>
       <c r="B91">
-        <v>744.26</v>
+        <v>732.97</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.2">
@@ -2753,7 +2729,7 @@
         <v>46258</v>
       </c>
       <c r="B92">
-        <v>739.27428571428572</v>
+        <v>733.59428571428577</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.2">
@@ -2761,7 +2737,7 @@
         <v>46259</v>
       </c>
       <c r="B93">
-        <v>734.70999999999992</v>
+        <v>732.67285714285708</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.2">
@@ -2769,7 +2745,7 @@
         <v>46260</v>
       </c>
       <c r="B94">
-        <v>730.94714285714281</v>
+        <v>730.05857142857144</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.2">
@@ -2777,7 +2753,7 @@
         <v>46261</v>
       </c>
       <c r="B95">
-        <v>728.8</v>
+        <v>726.15428571428572</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.2">
@@ -2785,7 +2761,7 @@
         <v>46262</v>
       </c>
       <c r="B96">
-        <v>728.38285714285723</v>
+        <v>721.13714285714286</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.2">
@@ -2793,7 +2769,7 @@
         <v>46265</v>
       </c>
       <c r="B97">
-        <v>729.41</v>
+        <v>716.22285714285715</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.2">
@@ -2801,7 +2777,7 @@
         <v>46266</v>
       </c>
       <c r="B98">
-        <v>731.39285714285722</v>
+        <v>712.4671428571429</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.2">
@@ -2809,7 +2785,7 @@
         <v>46267</v>
       </c>
       <c r="B99">
-        <v>732.97</v>
+        <v>710.84285714285716</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.2">
@@ -2817,7 +2793,7 @@
         <v>46268</v>
       </c>
       <c r="B100">
-        <v>733.59428571428577</v>
+        <v>712.14142857142861</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.2">
@@ -2825,7 +2801,7 @@
         <v>46269</v>
       </c>
       <c r="B101">
-        <v>732.67285714285708</v>
+        <v>716.02</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.2">
@@ -2833,7 +2809,7 @@
         <v>46272</v>
       </c>
       <c r="B102">
-        <v>730.05857142857144</v>
+        <v>722.3685714285715</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.2">
@@ -2841,7 +2817,7 @@
         <v>46273</v>
       </c>
       <c r="B103">
-        <v>726.15428571428572</v>
+        <v>730.36857142857139</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.2">
@@ -2849,7 +2825,7 @@
         <v>46274</v>
       </c>
       <c r="B104">
-        <v>721.13714285714286</v>
+        <v>738.93714285714282</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.2">
@@ -2857,7 +2833,7 @@
         <v>46275</v>
       </c>
       <c r="B105">
-        <v>716.22285714285715</v>
+        <v>747.03</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.2">
@@ -2865,7 +2841,7 @@
         <v>46276</v>
       </c>
       <c r="B106">
-        <v>712.4671428571429</v>
+        <v>753.04142857142847</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.2">
@@ -2873,7 +2849,7 @@
         <v>46279</v>
       </c>
       <c r="B107">
-        <v>710.84285714285716</v>
+        <v>756.48857142857139</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.2">
@@ -2881,7 +2857,7 @@
         <v>46280</v>
       </c>
       <c r="B108">
-        <v>712.14142857142861</v>
+        <v>757.07</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.2">
@@ -2889,7 +2865,7 @@
         <v>46281</v>
       </c>
       <c r="B109">
-        <v>716.02</v>
+        <v>755.06714285714293</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.2">
@@ -2897,7 +2873,7 @@
         <v>46282</v>
       </c>
       <c r="B110">
-        <v>722.3685714285715</v>
+        <v>751.33428571428567</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.2">
@@ -2905,71 +2881,47 @@
         <v>46283</v>
       </c>
       <c r="B111">
-        <v>730.36857142857139</v>
+        <v>746.31285714285718</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A112" s="2">
         <v>46286</v>
       </c>
-      <c r="B112">
-        <v>738.93714285714282</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A113" s="2">
         <v>46287</v>
       </c>
-      <c r="B113">
-        <v>747.03</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A114" s="2">
         <v>46288</v>
       </c>
-      <c r="B114">
-        <v>753.04142857142847</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A115" s="2">
         <v>46289</v>
       </c>
-      <c r="B115">
-        <v>756.48857142857139</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A116" s="2">
         <v>46290</v>
       </c>
-      <c r="B116">
-        <v>757.07</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A117" s="2">
         <v>46293</v>
       </c>
-      <c r="B117">
-        <v>755.06714285714293</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A118" s="2">
         <v>46294</v>
       </c>
-      <c r="B118">
-        <v>751.33428571428567</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A119" s="2">
         <v>46295</v>
-      </c>
-      <c r="B119">
-        <v>746.31285714285718</v>
       </c>
     </row>
   </sheetData>
